--- a/docs/station4/テスト設計書.xlsx
+++ b/docs/station4/テスト設計書.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="13560" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="認証機能" sheetId="1" r:id="rId1"/>
     <sheet name="検索機能" sheetId="2" r:id="rId2"/>
-    <sheet name="マップ機能" sheetId="3" r:id="rId3"/>
-    <sheet name="投稿作成機能" sheetId="4" r:id="rId4"/>
+    <sheet name="投稿作成機能" sheetId="4" r:id="rId3"/>
+    <sheet name="フォロー機能" sheetId="5" r:id="rId4"/>
+    <sheet name="いいね機能" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="162">
   <si>
     <t>ID</t>
   </si>
@@ -48,9 +49,6 @@
   </si>
   <si>
     <t>確認状態</t>
-  </si>
-  <si>
-    <t>優先度</t>
   </si>
   <si>
     <t>新規会員登録</t>
@@ -68,30 +66,18 @@
   </si>
   <si>
     <t>1.ユーザー登録画面を開く
-2.必須項目(メール、パスワード)を入力
-3.次へ進むボタンを押す
-4.必要項目(ユーザーID)を入力
-5.登録ボタンを押す</t>
+2.必須項目(ユーザーID、メール、パスワード)を入力
+3.登録ボタンを押す</t>
   </si>
   <si>
     <t>・登録完了
-・完了メッセージ表示
-・ログイン画面へ移行</t>
+・認証メール送信画面へ移行</t>
   </si>
   <si>
     <t>正常系</t>
   </si>
   <si>
-    <t>高</t>
-  </si>
-  <si>
     <t>UT-002</t>
-  </si>
-  <si>
-    <t>・任意フィールドが空</t>
-  </si>
-  <si>
-    <t>UT-003</t>
   </si>
   <si>
     <t>メール重複</t>
@@ -111,7 +97,7 @@
     <t>異常系</t>
   </si>
   <si>
-    <t>UT-004</t>
+    <t>UT-003</t>
   </si>
   <si>
     <t>メール形式の不備</t>
@@ -127,7 +113,7 @@
     <t>・エラーメッセージ表示</t>
   </si>
   <si>
-    <t>UT-005</t>
+    <t>UT-004</t>
   </si>
   <si>
     <t>パスワード強度不足</t>
@@ -140,7 +126,7 @@
 2.基準を満たさないパスワードで登録</t>
   </si>
   <si>
-    <t>UT-006</t>
+    <t>UT-005</t>
   </si>
   <si>
     <t>パスワード確認フィールドの失敗</t>
@@ -153,10 +139,36 @@
 2.確認フィールドで異なるパスワードを入力</t>
   </si>
   <si>
+    <t>UT-006</t>
+  </si>
+  <si>
+    <t>ユーザーID不備</t>
+  </si>
+  <si>
+    <t>・ユーザーIDが規定に沿っていない</t>
+  </si>
+  <si>
+    <t>1.ユーザー登録画面を開く
+2.基準を満たさないユーザーIDで登録</t>
+  </si>
+  <si>
+    <t>UT-007</t>
+  </si>
+  <si>
+    <t>ユーザーID重複</t>
+  </si>
+  <si>
+    <t>・登録済みユーザーID</t>
+  </si>
+  <si>
+    <t>1.ユーザー登録画面を開く
+2.登録済みユーザーIDで登録</t>
+  </si>
+  <si>
     <t>ユーザーログイン</t>
   </si>
   <si>
-    <t>UT-007</t>
+    <t>UT-008</t>
   </si>
   <si>
     <t>正常ログイン</t>
@@ -174,60 +186,91 @@
 ・投稿一覧画面へ移行</t>
   </si>
   <si>
-    <t>UT-008</t>
+    <t>UT-009</t>
   </si>
   <si>
     <t>パスワード不備</t>
   </si>
   <si>
-    <t>・正しいメール、間違ったパスワード</t>
+    <t>・間違ったパスワード</t>
   </si>
   <si>
     <t>・エラーメッセージ表示
 ・ログイン失敗</t>
   </si>
   <si>
-    <t>UT-009</t>
-  </si>
-  <si>
-    <t>バリデーションエラー</t>
-  </si>
-  <si>
-    <t>・フィールドが空</t>
-  </si>
-  <si>
-    <t>1.ログイン画面を開く
-3.ログインボタンを押す</t>
-  </si>
-  <si>
-    <t>・バリデーションエラー表示</t>
-  </si>
-  <si>
     <t>UT-010</t>
   </si>
   <si>
-    <t>正常検索</t>
-  </si>
-  <si>
-    <t>・投稿に存在するフリーワード
-・条件を選択</t>
-  </si>
-  <si>
-    <t>1.投稿検索画面を開く
-2.条件を選択、フリーワードを入力
-3.検索ボタンを押す</t>
-  </si>
-  <si>
-    <t>・検索結果表示</t>
+    <t>メールアドレス不備</t>
+  </si>
+  <si>
+    <t>・未登録メール</t>
   </si>
   <si>
     <t>UT-011</t>
   </si>
   <si>
-    <t>検索結果0</t>
-  </si>
-  <si>
-    <t>・投稿に存在しないフリーワード</t>
+    <t>ログアウト</t>
+  </si>
+  <si>
+    <t>・ログイン済み</t>
+  </si>
+  <si>
+    <t>1.プロフィール画面へ
+2.右上の設定ボタンを押す
+3.「ログアウト」をクリック
+4.確認メッセージ表示</t>
+  </si>
+  <si>
+    <t>・ログアウト完了
+・ログイン画面へ移行</t>
+  </si>
+  <si>
+    <t>UT-012</t>
+  </si>
+  <si>
+    <t>アカウント消去</t>
+  </si>
+  <si>
+    <t>1.プロフィール画面へ
+2.右上の設定ボタンを押す
+3.「アカウント消去」をクリック
+4.パスワードを入力
+5.確認メッセージ</t>
+  </si>
+  <si>
+    <t>・アカウント消去完了
+・新規登録画面へ移行</t>
+  </si>
+  <si>
+    <t>UT-013</t>
+  </si>
+  <si>
+    <t>アカウント消去失敗</t>
+  </si>
+  <si>
+    <t>・ログイン済み
+・間違ったパスワード</t>
+  </si>
+  <si>
+    <t>1.プロフィール画面へ
+2.右上の設定ボタンを押す
+3.「アカウント消去」をクリック
+4.間違ったパスワードを入力</t>
+  </si>
+  <si>
+    <t>・アカウント消去失敗
+・エラーメッセージ表示</t>
+  </si>
+  <si>
+    <t>UT-0114</t>
+  </si>
+  <si>
+    <t>フリーワード検索</t>
+  </si>
+  <si>
+    <t>・フリーワードを入力</t>
   </si>
   <si>
     <t>1.投稿検索画面を開く
@@ -235,10 +278,16 @@
 3.検索ボタンを押す</t>
   </si>
   <si>
-    <t>UT-012</t>
-  </si>
-  <si>
-    <t>・投稿が存在しない条件</t>
+    <t>・検索結果表示</t>
+  </si>
+  <si>
+    <t>UT-0115</t>
+  </si>
+  <si>
+    <t>条件検索</t>
+  </si>
+  <si>
+    <t>・条件を選択</t>
   </si>
   <si>
     <t>1.投稿検索画面を開く
@@ -246,141 +295,327 @@
 3.検索ボタンを押す</t>
   </si>
   <si>
-    <t>UT-013</t>
-  </si>
-  <si>
-    <t>・フィールド未入力</t>
+    <t>UT-0116</t>
+  </si>
+  <si>
+    <t>条件・フリーワード検索</t>
+  </si>
+  <si>
+    <t>・フリーワードを入力
+・条件を選択</t>
   </si>
   <si>
     <t>1.投稿検索画面を開く
-2.検索ボタンを押す</t>
-  </si>
-  <si>
-    <t>・バリディーションエラー表示</t>
-  </si>
-  <si>
-    <t>UT-014</t>
-  </si>
-  <si>
-    <t>GPS動作</t>
-  </si>
-  <si>
-    <t>・GPSオン</t>
-  </si>
-  <si>
-    <t>1.マップ画面を開く</t>
-  </si>
-  <si>
-    <t>・自分の位置情報が表示される</t>
-  </si>
-  <si>
-    <t>UT-015</t>
-  </si>
-  <si>
-    <t>GPS未動作</t>
-  </si>
-  <si>
-    <t>・GPSオフ</t>
-  </si>
-  <si>
-    <t>・自分の位置情報が表示されない
-・エラーメッセージの表示
-・デフォルトの地図を表示</t>
-  </si>
-  <si>
-    <t>UT-016</t>
+2.フリーワード、条件を選択
+3.検索ボタンを押す</t>
+  </si>
+  <si>
+    <t>UT-017</t>
   </si>
   <si>
     <t>下書き作成</t>
   </si>
   <si>
+    <t xml:space="preserve">・必要項目の記入
+・タビ状況：「準備中」or「旅行中」
+</t>
+  </si>
+  <si>
+    <t>1.投稿作成ボタンを押す
+2.必要項目を記入する
+3.タビ状況「準備中」or「旅行中」を選択
+4.作成ボタンを押す</t>
+  </si>
+  <si>
+    <t>・下書きに投稿が追加される</t>
+  </si>
+  <si>
+    <t>UT-018</t>
+  </si>
+  <si>
+    <t>公開投稿</t>
+  </si>
+  <si>
     <t>・必要項目の記入
-・ステータス：準備中or旅行中</t>
-  </si>
-  <si>
-    <t>1.プロフィール画面を開く
-2.投稿作成ボタンを押す
-3.必要項目を記入する
-4.ステータスを「準備中or旅行中」を選択
-5.作成ボタンを押す</t>
-  </si>
-  <si>
-    <t>・下書きに投稿が追加される</t>
-  </si>
-  <si>
-    <t>中</t>
-  </si>
-  <si>
-    <t>UT-017</t>
-  </si>
-  <si>
-    <t>他ユーザーへ投稿共有</t>
-  </si>
-  <si>
-    <t>・必要項目の記入
-・ステータス：「旅行済」「他ユーザーへ共有」</t>
-  </si>
-  <si>
-    <t>1.プロフィール画面を開く
-2.投稿作成ボタンを押す
-3.必要項目を記入する
-4.ステータスを「旅行済」「他ユーザーへ共有」を選択
-5.作成ボタンを押す</t>
+・タビ状況：「旅行済」
+・公開範囲設定：「公開」</t>
+  </si>
+  <si>
+    <t>1.投稿作成ボタンを押す
+2.必要項目を記入する
+3.ステータスは「旅行済」「公開」を選択
+4.作成ボタンを押す</t>
   </si>
   <si>
     <t>・自分のプロフィールに投稿が追加される
 ・タイムラインに投稿が表示される</t>
   </si>
   <si>
-    <t>UT-018</t>
-  </si>
-  <si>
-    <t>自分のプロフィールにのみ投稿を表示</t>
+    <t>UT-019</t>
+  </si>
+  <si>
+    <t>非公開投稿</t>
   </si>
   <si>
     <t>・必要項目の記入
-・ステータス：「旅行済」「自分のプロフィールのみに表示」</t>
-  </si>
-  <si>
-    <t>1.プロフィール画面を開く
-2.投稿作成ボタンを押す
-3.必要項目を記入する
-4.ステータスを「旅行済」「自分のプロフィールのみに表示」を選択
-5.作成ボタンを押す</t>
-  </si>
-  <si>
-    <t>・自分のプロフィールに投稿が追加される</t>
-  </si>
-  <si>
-    <t>UT-019</t>
+・タビ状況：「旅行済」
+・公開範囲設定：「非公開」</t>
+  </si>
+  <si>
+    <t>1.投稿作成ボタンを押す
+2.必要項目を記入する
+3.ステータスを「旅行済」「非公開」を選択
+4.作成ボタンを押す</t>
+  </si>
+  <si>
+    <t>・プロフィールの非公開投稿一覧に追加される
+・タイムラインには表示されない</t>
+  </si>
+  <si>
+    <t>UT-020</t>
+  </si>
+  <si>
+    <t>バリデーションエラー（必須項目）</t>
   </si>
   <si>
     <t>・必要項目が空</t>
   </si>
   <si>
-    <t>1.プロフィール画面を開く
-2.投稿作成ボタンを押す
-3.作成ボタンを押す</t>
-  </si>
-  <si>
-    <t>UT-020</t>
-  </si>
-  <si>
-    <t>旅程の時系列不備</t>
-  </si>
-  <si>
-    <t>・旅程作成で時系列が不自然</t>
-  </si>
-  <si>
-    <t>1.プロフィール画面を開く
-2.投稿作成ボタンを押す
-3.必要項目を記入
-4.旅程記入の際、前のスポットを訪れた時間よりも早い時間で次のスポットを記入
-5.作成ボタンを押す</t>
-  </si>
-  <si>
-    <t>・エラーメッセージ表示
-・作成失敗</t>
+    <t>1.投稿作成ボタンを押す
+2.作成ボタンを押す</t>
+  </si>
+  <si>
+    <t>・バリデーションエラー表示</t>
+  </si>
+  <si>
+    <t>UT-021</t>
+  </si>
+  <si>
+    <t>バリデーションエラー（タイトル文字数上限）</t>
+  </si>
+  <si>
+    <t>・タイトルはmax50文字</t>
+  </si>
+  <si>
+    <t>1.投稿作成ボタンを押す
+2.必要項目記入
+3.タイトルが51文字以上
+4.作成ボタンを押す</t>
+  </si>
+  <si>
+    <t>UT-022</t>
+  </si>
+  <si>
+    <t>バリデーションエラー（サブタイトル文字数上限）</t>
+  </si>
+  <si>
+    <t>・サブタイトルはmax50文字</t>
+  </si>
+  <si>
+    <t>1.投稿作成ボタンを押す
+2.必要項目記入
+3.サブタイトルが51文字以上
+4.作成ボタンを押す</t>
+  </si>
+  <si>
+    <t>UT-023</t>
+  </si>
+  <si>
+    <t>バリデーションエラー（タビ概要文字数上限）</t>
+  </si>
+  <si>
+    <t>・タビ概要はmax1000文字</t>
+  </si>
+  <si>
+    <t>1.投稿作成ボタンを押す
+2.必要項目記入
+3.タビ概要が1000文字以上
+4.作成ボタンを押す</t>
+  </si>
+  <si>
+    <t>UT-024</t>
+  </si>
+  <si>
+    <t>写真枚数制限</t>
+  </si>
+  <si>
+    <t>・写真の枚数制限は８枚</t>
+  </si>
+  <si>
+    <t>1.投稿作成ボタンを押す
+2.写真を９枚選択する</t>
+  </si>
+  <si>
+    <t>・エラーメッセージが表示
+・9枚目は選択されない</t>
+  </si>
+  <si>
+    <t>UT-025</t>
+  </si>
+  <si>
+    <t>下書きを公開投稿</t>
+  </si>
+  <si>
+    <t>・タビ状況：「旅行済」
+・公開範囲設定：「公開」</t>
+  </si>
+  <si>
+    <t>1.下書き一覧
+2.任意の投稿を選択
+3.ステータスを「旅行済」「公開」へ変更
+4.編集ボタンを押す</t>
+  </si>
+  <si>
+    <t>UT-026</t>
+  </si>
+  <si>
+    <t>下書きを非公開投稿</t>
+  </si>
+  <si>
+    <t>・タビ状況：「旅行済」
+・公開範囲設定：「非公開」</t>
+  </si>
+  <si>
+    <t>1.下書き一覧
+2.任意の投稿を選択
+3.ステータスを「旅行済」「非公開」へ変更
+4.編集ボタンを押す</t>
+  </si>
+  <si>
+    <t>UT-027</t>
+  </si>
+  <si>
+    <t>非公開投稿を公開する</t>
+  </si>
+  <si>
+    <t>・公開範囲設定：「非公開」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.プロフィール画面の非公開投稿一覧へ移動
+2.公開設定ボタンを押す
+</t>
+  </si>
+  <si>
+    <t>UT-028</t>
+  </si>
+  <si>
+    <t>公開投稿を非公開する</t>
+  </si>
+  <si>
+    <t>・公開範囲設定：「公開」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.プロフィール画面の投稿一覧へ移動
+2.公開設定ボタンを押す
+</t>
+  </si>
+  <si>
+    <t>UT-029</t>
+  </si>
+  <si>
+    <t>投稿を削除する</t>
+  </si>
+  <si>
+    <t>・タビ状況：「旅行済」</t>
+  </si>
+  <si>
+    <t>1.プロフィールの投稿一覧へ
+2.投稿の右下にある投稿消去ボタンを押す
+3.確認メッセージ</t>
+  </si>
+  <si>
+    <t>・プロフィール画面、タイムラインから消える</t>
+  </si>
+  <si>
+    <t>UT-030</t>
+  </si>
+  <si>
+    <t>下書きを削除する</t>
+  </si>
+  <si>
+    <t>・タビ状況：「準備中」or「旅行中」</t>
+  </si>
+  <si>
+    <t>1.下書き一覧へ
+2.各下書きの消去ボタンを押す
+3.確認メッセージ</t>
+  </si>
+  <si>
+    <t>・下書き一覧から消える</t>
+  </si>
+  <si>
+    <t>UT-031</t>
+  </si>
+  <si>
+    <t>フォローする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・未フォローのユーザー
+</t>
+  </si>
+  <si>
+    <t>1.他ユーザーのプロフィール画面へ
+2.フォローボタンを押す</t>
+  </si>
+  <si>
+    <t>・自分のフォロー欄にフォローしたユーザーが表示される。フォロー数1増加
+・相手のフォロワー欄に自アカウントが表示される。フォロワー数1増加
+・フォローしたユーザーの投稿が、フォロー中タイムラインに表示される。</t>
+  </si>
+  <si>
+    <t>UT-032</t>
+  </si>
+  <si>
+    <t>フォローを外す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・フォロー中のユーザー
+</t>
+  </si>
+  <si>
+    <t>・自分のフォロー欄にフォロー解除したユーザーが消える。フォロー数1減少。
+・相手のフォロワー欄から自アカウントが消える。フォロワー数1減少。
+・フォロー解除したユーザーの投稿が、フォロー中タイムラインから消える。</t>
+  </si>
+  <si>
+    <t>UT-033</t>
+  </si>
+  <si>
+    <t>投稿にいいねする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・未いいねの投稿
+</t>
+  </si>
+  <si>
+    <t>1.投稿一覧へ
+2.任意の投稿をクリック
+3.投稿詳細画面でいいねボタンを押す</t>
+  </si>
+  <si>
+    <t>・いいねマークに色がつく
+・いいね数が1増加
+・いいねした投稿一覧に追加される</t>
+  </si>
+  <si>
+    <t>UT-034</t>
+  </si>
+  <si>
+    <t>投稿のいいね解除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・いいね中の投稿
+</t>
+  </si>
+  <si>
+    <t>1.投稿一覧へ
+2.いいね中の投稿をクリック
+3.投稿詳細画面でいいねボタンを押す</t>
+  </si>
+  <si>
+    <t>・いいねマークの色が消える
+・いいね数が1減少
+・いいねした投稿一覧から消える</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1027,7 +1262,19 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1562,18 +1809,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.7692307692308" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="36.5288461538462" customWidth="1"/>
+    <col min="3" max="3" width="40.8269230769231" customWidth="1"/>
     <col min="4" max="4" width="48.6346153846154" customWidth="1"/>
     <col min="5" max="5" width="31.9134615384615" customWidth="1"/>
     <col min="6" max="6" width="10.3076923076923" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1592,134 +1839,116 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" ht="68" spans="1:6">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" ht="84" spans="1:7">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="4" ht="34" spans="1:6">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" ht="84" spans="1:7">
-      <c r="A4" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="34" spans="1:7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="34" spans="1:6">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="34" spans="1:7">
+    </row>
+    <row r="6" ht="34" spans="1:6">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="34" spans="1:7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="34" spans="1:6">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
+      <c r="E7" t="s">
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="34" spans="1:7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1" spans="1:6">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1729,91 +1958,159 @@
       <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="1:6">
       <c r="A9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" ht="51" spans="1:7">
-      <c r="A10" t="s">
+      <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="2" t="s">
+    </row>
+    <row r="11" ht="51" spans="1:6">
+      <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="51" spans="1:7">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="34" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="51" spans="1:6">
       <c r="A12" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="51" spans="1:6">
+      <c r="A13" t="s">
         <v>50</v>
       </c>
-      <c r="F12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" ht="68" spans="1:6">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="84" spans="1:6">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="68" spans="1:6">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1825,8 +2122,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
     <col min="2" max="2" width="24.8461538461538" customWidth="1"/>
@@ -1835,7 +2132,7 @@
     <col min="5" max="5" width="30.3076923076923" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1854,100 +2151,65 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="51" spans="1:7">
+    </row>
+    <row r="2" ht="51" spans="1:6">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" ht="51" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="51" spans="1:6">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="51" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="51" spans="1:6">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
+        <v>77</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="34" spans="1:7">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1959,17 +2221,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
-    <col min="2" max="2" width="14.6923076923077" customWidth="1"/>
-    <col min="3" max="3" width="30.9615384615385" customWidth="1"/>
-    <col min="4" max="4" width="34.6153846153846" customWidth="1"/>
-    <col min="5" max="5" width="35.3846153846154" customWidth="1"/>
+    <col min="2" max="2" width="56.3846153846154" customWidth="1"/>
+    <col min="3" max="3" width="61.375" customWidth="1"/>
+    <col min="4" max="4" width="82.0384615384615" customWidth="1"/>
+    <col min="5" max="5" width="48.0769230769231" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1988,54 +2250,285 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="17" spans="1:7">
+    </row>
+    <row r="2" ht="68" spans="1:6">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" ht="51" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="68" spans="1:6">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="68" spans="1:6">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="34" spans="1:6">
+      <c r="A5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="68" spans="1:6">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="68" spans="1:6">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="68" spans="1:6">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="1:6">
+      <c r="A9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="68" spans="1:6">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" ht="68" spans="1:6">
+      <c r="A11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="51" spans="1:6">
+      <c r="A12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="51" spans="1:6">
+      <c r="A13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="51" spans="1:6">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="51" spans="1:6">
+      <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2047,17 +2540,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
-    <col min="2" max="2" width="44.2307692307692" customWidth="1"/>
-    <col min="3" max="3" width="61.375" customWidth="1"/>
-    <col min="4" max="4" width="82.0384615384615" customWidth="1"/>
-    <col min="5" max="5" width="44.7115384615385" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="43.4230769230769" customWidth="1"/>
+    <col min="4" max="4" width="42.1442307692308" customWidth="1"/>
+    <col min="5" max="5" width="80.6634615384615" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2076,123 +2569,124 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="84" spans="1:7">
+    </row>
+    <row r="2" ht="51" spans="1:6">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>145</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" ht="84" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="51" spans="1:6">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>86</v>
+        <v>149</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" ht="84" spans="1:7">
-      <c r="A4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" ht="51" spans="1:7">
-      <c r="A5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="84" spans="1:7">
-      <c r="A6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
+    <col min="2" max="2" width="21.4711538461538" customWidth="1"/>
+    <col min="3" max="3" width="36.0480769230769" customWidth="1"/>
+    <col min="4" max="4" width="36.8557692307692" customWidth="1"/>
+    <col min="5" max="5" width="73.7115384615385" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="51" spans="1:6">
+      <c r="A2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="51" spans="1:6">
+      <c r="A3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/station4/テスト設計書.xlsx
+++ b/docs/station4/テスト設計書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13560" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="13560" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="認証機能" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="164">
   <si>
     <t>ID</t>
   </si>
@@ -270,7 +270,8 @@
     <t>フリーワード検索</t>
   </si>
   <si>
-    <t>・フリーワードを入力</t>
+    <t>・フリーワードを入力
+・完全一致</t>
   </si>
   <si>
     <t>1.投稿検索画面を開く
@@ -308,6 +309,12 @@
     <t>1.投稿検索画面を開く
 2.フリーワード、条件を選択
 3.検索ボタンを押す</t>
+  </si>
+  <si>
+    <t>空白検索</t>
+  </si>
+  <si>
+    <t>セキュリティ対策</t>
   </si>
   <si>
     <t>UT-017</t>
@@ -2122,8 +2129,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
     <col min="2" max="2" width="24.8461538461538" customWidth="1"/>
@@ -2210,6 +2217,16 @@
       </c>
       <c r="F4" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2253,19 +2270,19 @@
     </row>
     <row r="2" ht="68" spans="1:6">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -2273,19 +2290,19 @@
     </row>
     <row r="3" ht="68" spans="1:6">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -2293,19 +2310,19 @@
     </row>
     <row r="4" ht="68" spans="1:6">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -2313,19 +2330,19 @@
     </row>
     <row r="5" ht="34" spans="1:6">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -2333,19 +2350,19 @@
     </row>
     <row r="6" ht="68" spans="1:6">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" t="s">
         <v>101</v>
-      </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" t="s">
-        <v>99</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -2353,19 +2370,19 @@
     </row>
     <row r="7" ht="68" spans="1:6">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -2373,19 +2390,19 @@
     </row>
     <row r="8" ht="68" spans="1:6">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -2393,19 +2410,19 @@
     </row>
     <row r="9" ht="34" spans="1:6">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -2413,19 +2430,19 @@
     </row>
     <row r="10" ht="68" spans="1:6">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -2433,19 +2450,19 @@
     </row>
     <row r="11" ht="68" spans="1:6">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -2453,19 +2470,19 @@
     </row>
     <row r="12" ht="51" spans="1:6">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -2473,19 +2490,19 @@
     </row>
     <row r="13" ht="51" spans="1:6">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -2493,19 +2510,19 @@
     </row>
     <row r="14" ht="51" spans="1:6">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -2513,19 +2530,19 @@
     </row>
     <row r="15" ht="51" spans="1:6">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -2572,19 +2589,19 @@
     </row>
     <row r="2" ht="51" spans="1:6">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -2592,19 +2609,19 @@
     </row>
     <row r="3" ht="51" spans="1:6">
       <c r="A3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -2651,19 +2668,19 @@
     </row>
     <row r="2" ht="51" spans="1:6">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -2671,19 +2688,19 @@
     </row>
     <row r="3" ht="51" spans="1:6">
       <c r="A3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -2691,6 +2708,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/docs/station4/テスト設計書.xlsx
+++ b/docs/station4/テスト設計書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13560" activeTab="1"/>
+    <workbookView windowWidth="28000" windowHeight="11540"/>
   </bookViews>
   <sheets>
     <sheet name="認証機能" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="197">
   <si>
     <t>ID</t>
   </si>
@@ -264,6 +264,48 @@
 ・エラーメッセージ表示</t>
   </si>
   <si>
+    <t>セキュリティ対策</t>
+  </si>
+  <si>
+    <t>TC-A-01</t>
+  </si>
+  <si>
+    <t>ログインフォームでのSQLi</t>
+  </si>
+  <si>
+    <t>1.ログイン画面
+2.メール欄に admin' OR '1'='1 / パスワード欄に任意 を入力</t>
+  </si>
+  <si>
+    <t>・認証バイパス不可。詳細なDBエラーや内部情報は返さない。</t>
+  </si>
+  <si>
+    <t>TC-A-02</t>
+  </si>
+  <si>
+    <t>ログインフォームでの反射型 XSS</t>
+  </si>
+  <si>
+    <t>1.ログイン画面
+2.メール欄に&lt;script&gt;alert(1)&lt;/script&gt; を入力し失敗ログイン</t>
+  </si>
+  <si>
+    <t>・スクリプトが実行されない。</t>
+  </si>
+  <si>
+    <t>TC-A-03</t>
+  </si>
+  <si>
+    <t>パスワード欄に対するSQLi</t>
+  </si>
+  <si>
+    <t>1.ログイン画面
+2.パスワード欄に ') OR '1'='1 を入力</t>
+  </si>
+  <si>
+    <t>認証バイパス不可。サーバは汎用エラーメッセージを返し、内部エラーを露出しない。</t>
+  </si>
+  <si>
     <t>UT-0114</t>
   </si>
   <si>
@@ -311,10 +353,46 @@
 3.検索ボタンを押す</t>
   </si>
   <si>
+    <t>UT-0117</t>
+  </si>
+  <si>
     <t>空白検索</t>
   </si>
   <si>
-    <t>セキュリティ対策</t>
+    <t>・条件・フリーワード設定しない</t>
+  </si>
+  <si>
+    <t>1.投稿検索画面を開く
+2.検索ボタンを押す</t>
+  </si>
+  <si>
+    <t>・全ての投稿表示</t>
+  </si>
+  <si>
+    <t>TC-S-01</t>
+  </si>
+  <si>
+    <t>検索クエリ（GET）に対する反射型 XSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.フリーワードフォームに以下を入力して検索
+&lt;script&gt;alert(1)&lt;/script&gt;
+</t>
+  </si>
+  <si>
+    <t>・ペイロードが実行されない。表示箇所はエスケープされる</t>
+  </si>
+  <si>
+    <t>TC-S-02</t>
+  </si>
+  <si>
+    <t>検索パラメータによるSQLi</t>
+  </si>
+  <si>
+    <t>1.q パラメータに test' OR '1'='1 等を与え検索</t>
+  </si>
+  <si>
+    <t>・攻撃によってクエリ結果が汚染されない。</t>
   </si>
   <si>
     <t>UT-017</t>
@@ -549,6 +627,41 @@
   </si>
   <si>
     <t>・下書き一覧から消える</t>
+  </si>
+  <si>
+    <t>TC-P-01:</t>
+  </si>
+  <si>
+    <t>投稿本文に対する保存型 XSS</t>
+  </si>
+  <si>
+    <t>・ログイン済みユーザ</t>
+  </si>
+  <si>
+    <t>1.投稿作成画面にアクセス
+2.タビ概要に以下を投稿して保存する
+ペイロード例（簡易）: &lt;script&gt;alert('XSS')&lt;/script&gt;
+ペイロード例（HTML属性型）: "&gt;&lt;img src=x onerror=alert('XSS')&gt;
+3.作成した投稿を一覧／詳細で表示</t>
+  </si>
+  <si>
+    <t>・ペイロードがブラウザで実行されない（アラートが出ない）</t>
+  </si>
+  <si>
+    <t>TC-P-02</t>
+  </si>
+  <si>
+    <t>投稿本文に対するSQLインジェクション</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.投稿作成画面にアクセス
+2.タビ概要に以下を投稿して保存する
+3.投稿本文に SQLi の試験文字列を投入し保存（POST）
+例：test'; SELECT version(); -- ／' OR '1'='1／時間型：' OR SLEEP(5) -- </t>
+  </si>
+  <si>
+    <t>DB のエラーが露出しないこと。
+レスポンスは通常通りで、SLEEP 等で遅延が発生しない（パラメタ化済み）</t>
   </si>
   <si>
     <t>UT-031</t>
@@ -1261,7 +1374,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1274,14 +1387,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1816,11 +1926,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.7692307692308" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="49.3076923076923" customWidth="1"/>
     <col min="3" max="3" width="40.8269230769231" customWidth="1"/>
     <col min="4" max="4" width="48.6346153846154" customWidth="1"/>
     <col min="5" max="5" width="31.9134615384615" customWidth="1"/>
@@ -1848,7 +1958,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3"/>
@@ -1996,7 +2106,7 @@
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2070,10 +2180,10 @@
       <c r="C14" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F14" t="s">
@@ -2090,10 +2200,10 @@
       <c r="C15" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F15" t="s">
@@ -2107,18 +2217,77 @@
       <c r="B16" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
       </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" ht="51" spans="1:6">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" ht="51" spans="1:6">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" ht="51" spans="1:6">
+      <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2129,14 +2298,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
-    <col min="2" max="2" width="24.8461538461538" customWidth="1"/>
+    <col min="2" max="2" width="44.0769230769231" customWidth="1"/>
     <col min="3" max="3" width="32.7211538461538" customWidth="1"/>
-    <col min="4" max="4" width="40.4038461538462" customWidth="1"/>
-    <col min="5" max="5" width="30.3076923076923" customWidth="1"/>
+    <col min="4" max="4" width="50.6923076923077" customWidth="1"/>
+    <col min="5" max="5" width="85.4615384615385" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2161,19 +2330,19 @@
     </row>
     <row r="2" ht="51" spans="1:6">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -2181,19 +2350,19 @@
     </row>
     <row r="3" ht="51" spans="1:6">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -2201,32 +2370,81 @@
     </row>
     <row r="4" ht="51" spans="1:6">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
+    <row r="5" ht="34" spans="1:6">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
       <c r="B5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>81</v>
+        <v>94</v>
+      </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" ht="51" spans="1:6">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:6">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2238,11 +2456,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
-    <col min="2" max="2" width="56.3846153846154" customWidth="1"/>
+    <col min="1" max="1" width="9.46153846153846" customWidth="1"/>
+    <col min="2" max="2" width="68.4615384615385" customWidth="1"/>
     <col min="3" max="3" width="61.375" customWidth="1"/>
     <col min="4" max="4" width="82.0384615384615" customWidth="1"/>
     <col min="5" max="5" width="48.0769230769231" customWidth="1"/>
@@ -2270,19 +2488,19 @@
     </row>
     <row r="2" ht="68" spans="1:6">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -2290,19 +2508,19 @@
     </row>
     <row r="3" ht="68" spans="1:6">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -2310,19 +2528,19 @@
     </row>
     <row r="4" ht="68" spans="1:6">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -2330,19 +2548,19 @@
     </row>
     <row r="5" ht="34" spans="1:6">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -2350,19 +2568,19 @@
     </row>
     <row r="6" ht="68" spans="1:6">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -2370,19 +2588,19 @@
     </row>
     <row r="7" ht="68" spans="1:6">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -2390,19 +2608,19 @@
     </row>
     <row r="8" ht="68" spans="1:6">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -2410,19 +2628,19 @@
     </row>
     <row r="9" ht="34" spans="1:6">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>116</v>
+        <v>139</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -2430,19 +2648,19 @@
     </row>
     <row r="10" ht="68" spans="1:6">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>91</v>
+        <v>144</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -2450,19 +2668,19 @@
     </row>
     <row r="11" ht="68" spans="1:6">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>96</v>
+        <v>148</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -2470,19 +2688,19 @@
     </row>
     <row r="12" ht="51" spans="1:6">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>91</v>
+        <v>153</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -2490,19 +2708,19 @@
     </row>
     <row r="13" ht="51" spans="1:6">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>96</v>
+        <v>157</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -2510,19 +2728,19 @@
     </row>
     <row r="14" ht="51" spans="1:6">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>138</v>
+        <v>161</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="E14" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -2530,21 +2748,66 @@
     </row>
     <row r="15" ht="51" spans="1:6">
       <c r="A15" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>143</v>
+        <v>166</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="E15" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="F15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" ht="84" spans="1:6">
+      <c r="A17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="68" spans="1:6">
+      <c r="A18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2557,11 +2820,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="51.5384615384615" customWidth="1"/>
     <col min="3" max="3" width="43.4230769230769" customWidth="1"/>
     <col min="4" max="4" width="42.1442307692308" customWidth="1"/>
     <col min="5" max="5" width="80.6634615384615" customWidth="1"/>
@@ -2589,19 +2852,19 @@
     </row>
     <row r="2" ht="51" spans="1:6">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -2609,23 +2872,26 @@
     </row>
     <row r="3" ht="51" spans="1:6">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>152</v>
+        <v>184</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2636,8 +2902,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.23076923076923" customWidth="1"/>
     <col min="2" max="2" width="21.4711538461538" customWidth="1"/>
@@ -2668,19 +2934,19 @@
     </row>
     <row r="2" ht="51" spans="1:6">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -2688,23 +2954,26 @@
     </row>
     <row r="3" ht="51" spans="1:6">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>161</v>
+        <v>193</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/station4/テスト設計書.xlsx
+++ b/docs/station4/テスト設計書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="11540"/>
+    <workbookView windowWidth="28000" windowHeight="11540" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="認証機能" sheetId="1" r:id="rId1"/>
@@ -909,12 +909,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1250,7 +1256,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1274,16 +1280,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1292,94 +1298,97 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1958,27 +1967,27 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" ht="68" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
@@ -1986,19 +1995,19 @@
       </c>
     </row>
     <row r="4" ht="34" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F4" t="s">
@@ -2006,19 +2015,19 @@
       </c>
     </row>
     <row r="5" ht="34" spans="1:6">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F5" t="s">
@@ -2026,19 +2035,19 @@
       </c>
     </row>
     <row r="6" ht="34" spans="1:6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F6" t="s">
@@ -2046,7 +2055,7 @@
       </c>
     </row>
     <row r="7" ht="34" spans="1:6">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
@@ -2055,7 +2064,7 @@
       <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E7" t="s">
@@ -2066,7 +2075,7 @@
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:6">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B8" t="s">
@@ -2075,7 +2084,7 @@
       <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E8" t="s">
@@ -2086,7 +2095,7 @@
       </c>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B9" t="s">
@@ -2095,7 +2104,7 @@
       <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E9" t="s">
@@ -2106,12 +2115,12 @@
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" ht="51" spans="1:6">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B11" t="s">
@@ -2120,10 +2129,10 @@
       <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
@@ -2131,19 +2140,19 @@
       </c>
     </row>
     <row r="12" ht="51" spans="1:6">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F12" t="s">
@@ -2151,7 +2160,7 @@
       </c>
     </row>
     <row r="13" ht="51" spans="1:6">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B13" t="s">
@@ -2160,10 +2169,10 @@
       <c r="C13" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F13" t="s">
@@ -2171,7 +2180,7 @@
       </c>
     </row>
     <row r="14" ht="68" spans="1:6">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B14" t="s">
@@ -2180,10 +2189,10 @@
       <c r="C14" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F14" t="s">
@@ -2191,7 +2200,7 @@
       </c>
     </row>
     <row r="15" ht="84" spans="1:6">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B15" t="s">
@@ -2200,10 +2209,10 @@
       <c r="C15" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>61</v>
       </c>
       <c r="F15" t="s">
@@ -2211,19 +2220,19 @@
       </c>
     </row>
     <row r="16" ht="68" spans="1:6">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B16" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>66</v>
       </c>
       <c r="F16" t="s">
@@ -2231,21 +2240,21 @@
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="20" ht="51" spans="1:6">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B20" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>71</v>
       </c>
       <c r="F20" t="s">
@@ -2253,13 +2262,13 @@
       </c>
     </row>
     <row r="21" ht="51" spans="1:6">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B21" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>74</v>
       </c>
       <c r="E21" t="s">
@@ -2270,16 +2279,16 @@
       </c>
     </row>
     <row r="22" ht="51" spans="1:6">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>79</v>
       </c>
       <c r="F22" t="s">
@@ -2287,7 +2296,7 @@
       </c>
     </row>
     <row r="24" spans="5:5">
-      <c r="E24" s="5"/>
+      <c r="E24" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2329,19 +2338,19 @@
       </c>
     </row>
     <row r="2" ht="51" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B2" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>84</v>
       </c>
       <c r="F2" t="s">
@@ -2349,19 +2358,19 @@
       </c>
     </row>
     <row r="3" ht="51" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>84</v>
       </c>
       <c r="F3" t="s">
@@ -2369,19 +2378,19 @@
       </c>
     </row>
     <row r="4" ht="51" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>84</v>
       </c>
       <c r="F4" t="s">
@@ -2389,7 +2398,7 @@
       </c>
     </row>
     <row r="5" ht="34" spans="1:6">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B5" t="s">
@@ -2398,7 +2407,7 @@
       <c r="C5" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>96</v>
       </c>
       <c r="E5" t="s">
@@ -2409,21 +2418,21 @@
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="8" ht="51" spans="1:6">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B8" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F8" t="s">
@@ -2431,13 +2440,13 @@
       </c>
     </row>
     <row r="9" ht="17" spans="1:6">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B9" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E9" t="s">
@@ -2487,19 +2496,19 @@
       </c>
     </row>
     <row r="2" ht="68" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>110</v>
       </c>
       <c r="F2" t="s">
@@ -2507,19 +2516,19 @@
       </c>
     </row>
     <row r="3" ht="68" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B3" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>115</v>
       </c>
       <c r="F3" t="s">
@@ -2527,19 +2536,19 @@
       </c>
     </row>
     <row r="4" ht="68" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B4" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>120</v>
       </c>
       <c r="F4" t="s">
@@ -2547,7 +2556,7 @@
       </c>
     </row>
     <row r="5" ht="34" spans="1:6">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B5" t="s">
@@ -2556,7 +2565,7 @@
       <c r="C5" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>124</v>
       </c>
       <c r="E5" t="s">
@@ -2567,7 +2576,7 @@
       </c>
     </row>
     <row r="6" ht="68" spans="1:6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B6" t="s">
@@ -2576,7 +2585,7 @@
       <c r="C6" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>129</v>
       </c>
       <c r="E6" t="s">
@@ -2587,7 +2596,7 @@
       </c>
     </row>
     <row r="7" ht="68" spans="1:6">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B7" t="s">
@@ -2596,7 +2605,7 @@
       <c r="C7" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>133</v>
       </c>
       <c r="E7" t="s">
@@ -2607,7 +2616,7 @@
       </c>
     </row>
     <row r="8" ht="68" spans="1:6">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B8" t="s">
@@ -2616,7 +2625,7 @@
       <c r="C8" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>137</v>
       </c>
       <c r="E8" t="s">
@@ -2627,19 +2636,19 @@
       </c>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B9" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>142</v>
       </c>
       <c r="F9" t="s">
@@ -2647,19 +2656,19 @@
       </c>
     </row>
     <row r="10" ht="68" spans="1:6">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>143</v>
       </c>
       <c r="B10" t="s">
         <v>144</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>115</v>
       </c>
       <c r="F10" t="s">
@@ -2667,19 +2676,19 @@
       </c>
     </row>
     <row r="11" ht="68" spans="1:6">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B11" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>120</v>
       </c>
       <c r="F11" t="s">
@@ -2687,7 +2696,7 @@
       </c>
     </row>
     <row r="12" ht="51" spans="1:6">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B12" t="s">
@@ -2696,10 +2705,10 @@
       <c r="C12" t="s">
         <v>153</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>115</v>
       </c>
       <c r="F12" t="s">
@@ -2707,7 +2716,7 @@
       </c>
     </row>
     <row r="13" ht="51" spans="1:6">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B13" t="s">
@@ -2716,10 +2725,10 @@
       <c r="C13" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>120</v>
       </c>
       <c r="F13" t="s">
@@ -2727,7 +2736,7 @@
       </c>
     </row>
     <row r="14" ht="51" spans="1:6">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B14" t="s">
@@ -2736,7 +2745,7 @@
       <c r="C14" t="s">
         <v>161</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>162</v>
       </c>
       <c r="E14" t="s">
@@ -2747,7 +2756,7 @@
       </c>
     </row>
     <row r="15" ht="51" spans="1:6">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B15" t="s">
@@ -2756,7 +2765,7 @@
       <c r="C15" t="s">
         <v>166</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>167</v>
       </c>
       <c r="E15" t="s">
@@ -2772,7 +2781,7 @@
       </c>
     </row>
     <row r="17" ht="84" spans="1:6">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>169</v>
       </c>
       <c r="B17" t="s">
@@ -2781,10 +2790,10 @@
       <c r="C17" t="s">
         <v>171</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>173</v>
       </c>
       <c r="F17" t="s">
@@ -2792,7 +2801,7 @@
       </c>
     </row>
     <row r="18" ht="68" spans="1:6">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B18" t="s">
@@ -2801,10 +2810,10 @@
       <c r="C18" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>177</v>
       </c>
       <c r="F18" t="s">
@@ -2851,19 +2860,19 @@
       </c>
     </row>
     <row r="2" ht="51" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>178</v>
       </c>
       <c r="B2" t="s">
         <v>179</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>182</v>
       </c>
       <c r="F2" t="s">
@@ -2871,19 +2880,19 @@
       </c>
     </row>
     <row r="3" ht="51" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>183</v>
       </c>
       <c r="B3" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>186</v>
       </c>
       <c r="F3" t="s">
@@ -2891,7 +2900,7 @@
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2933,19 +2942,19 @@
       </c>
     </row>
     <row r="2" ht="51" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B2" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>191</v>
       </c>
       <c r="F2" t="s">
@@ -2953,19 +2962,19 @@
       </c>
     </row>
     <row r="3" ht="51" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>192</v>
       </c>
       <c r="B3" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>196</v>
       </c>
       <c r="F3" t="s">
@@ -2973,7 +2982,7 @@
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
